--- a/utils/monday_sprint_sprint_2023-06.xlsx
+++ b/utils/monday_sprint_sprint_2023-06.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="113">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Abertura</t>
+    <t>Entrada Sprint</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,6 +51,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>SLA (15 dias)</t>
+  </si>
+  <si>
     <t>Semana</t>
   </si>
   <si>
@@ -60,27 +63,45 @@
     <t>3877</t>
   </si>
   <si>
-    <t>Sprint 2023-06</t>
+    <t>Setor não informado</t>
   </si>
   <si>
     <t>Novo Recurso</t>
   </si>
   <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Movimentação de conjuntos pela etiqueta amarela</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>20/06/2021</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Movimentação de conjuntos pela etiqueta amarela</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
     <t>Feito</t>
   </si>
   <si>
+    <t>Não</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
+    <t>Junho</t>
+  </si>
+  <si>
     <t>18856</t>
   </si>
   <si>
@@ -93,9 +114,15 @@
     <t>Média</t>
   </si>
   <si>
+    <t>27/02/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
     <t>4053209057</t>
   </si>
   <si>
@@ -114,21 +141,33 @@
     <t>Modificar saída de dados apontamento células.</t>
   </si>
   <si>
+    <t>28/02/2023</t>
+  </si>
+  <si>
     <t>18941</t>
   </si>
   <si>
     <t>Sistema para horas Parte 01</t>
   </si>
   <si>
+    <t>02/03/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
+    <t>Março</t>
+  </si>
+  <si>
     <t>19010</t>
   </si>
   <si>
     <t>Campo para preenchimento de tempo de desmoldagem.</t>
   </si>
   <si>
+    <t>07/03/2023</t>
+  </si>
+  <si>
     <t>18907</t>
   </si>
   <si>
@@ -159,6 +198,9 @@
     <t>Atualização dos Fluxos Pré Produtivos.</t>
   </si>
   <si>
+    <t>08/03/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -168,6 +210,9 @@
     <t>Sistema de apontamento das linhas</t>
   </si>
   <si>
+    <t>10/03/2023</t>
+  </si>
+  <si>
     <t>18892</t>
   </si>
   <si>
@@ -186,6 +231,9 @@
     <t>4135163187</t>
   </si>
   <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
     <t>4135163380</t>
   </si>
   <si>
@@ -195,15 +243,24 @@
     <t>Melhoria lançamento fiscal de consignados</t>
   </si>
   <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
     <t>19234</t>
   </si>
   <si>
     <t>Alteração regra de preenchimento integração NF entrada para Benner</t>
   </si>
   <si>
+    <t>16/03/2023</t>
+  </si>
+  <si>
     <t>Sistema para horas Parte 02</t>
   </si>
   <si>
+    <t>21/03/2023</t>
+  </si>
+  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
@@ -249,7 +306,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA</t>
+    <t>Cumprimento SLA (15 dias)</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -270,10 +327,10 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Abertos</t>
   </si>
   <si>
     <t>Impedimento</t>
@@ -711,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -721,13 +778,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -770,841 +829,901 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="J3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="M17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="M18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="M19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="M20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1620,23 +1739,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -1644,16 +1763,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1664,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>46.37</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -1672,12 +1791,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K22">
         <v>19</v>
@@ -1685,7 +1804,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1693,7 +1812,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1724,12 +1843,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="B2">
         <v>19</v>
@@ -1743,7 +1862,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>46.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -1753,60 +1872,60 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N10">
         <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q10">
         <v>6</v>
@@ -1814,31 +1933,31 @@
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="K11">
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1846,25 +1965,31 @@
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H12">
         <v>15</v>
       </c>
+      <c r="J12" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -1872,25 +1997,25 @@
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -1898,13 +2023,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1912,7 +2037,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1920,7 +2045,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1928,7 +2053,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1936,7 +2061,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -1947,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -1955,142 +2080,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2023-06.xlsx
+++ b/utils/monday_sprint_sprint_2023-06.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="119">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>3877</t>
+    <t>1407234730</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>20/06/2021</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>25/03/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>18856</t>
+    <t>4050810011</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -117,6 +117,9 @@
     <t>27/02/2023</t>
   </si>
   <si>
+    <t>21/03/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
@@ -135,7 +138,10 @@
     <t>Não definida</t>
   </si>
   <si>
-    <t>18891</t>
+    <t>26/03/2023</t>
+  </si>
+  <si>
+    <t>4062898346</t>
   </si>
   <si>
     <t>Modificar saída de dados apontamento células.</t>
@@ -144,7 +150,7 @@
     <t>28/02/2023</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>4076300339</t>
   </si>
   <si>
     <t>Sistema para horas Parte 01</t>
@@ -159,7 +165,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>19010</t>
+    <t>4100917795</t>
   </si>
   <si>
     <t>Campo para preenchimento de tempo de desmoldagem.</t>
@@ -168,31 +174,40 @@
     <t>07/03/2023</t>
   </si>
   <si>
-    <t>18907</t>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>4101206752</t>
   </si>
   <si>
     <t>Inclusão de Tarefas Preventivas na OS e Botão de Imprimir todas.</t>
   </si>
   <si>
-    <t>18929</t>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>4101313357</t>
   </si>
   <si>
     <t>Divergência do Relatório de Notas fiscais e Resumo de faturamento.</t>
   </si>
   <si>
-    <t>18977</t>
+    <t>4101571809</t>
   </si>
   <si>
     <t>Fluxo / Entrada de peças.</t>
   </si>
   <si>
-    <t>18981</t>
+    <t>4101615174</t>
   </si>
   <si>
     <t>Ajuste diferencial de ICMS.</t>
   </si>
   <si>
-    <t>19081</t>
+    <t>13/03/2023</t>
+  </si>
+  <si>
+    <t>4109806347</t>
   </si>
   <si>
     <t>Atualização dos Fluxos Pré Produtivos.</t>
@@ -201,10 +216,13 @@
     <t>08/03/2023</t>
   </si>
   <si>
+    <t>23/03/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>19113</t>
+    <t>4123598492</t>
   </si>
   <si>
     <t>Sistema de apontamento das linhas</t>
@@ -213,7 +231,7 @@
     <t>10/03/2023</t>
   </si>
   <si>
-    <t>18892</t>
+    <t>4123710182</t>
   </si>
   <si>
     <t>Correção</t>
@@ -222,7 +240,7 @@
     <t>Status clientes.</t>
   </si>
   <si>
-    <t>19121</t>
+    <t>4123861292</t>
   </si>
   <si>
     <t>Filtro por CFOP</t>
@@ -231,22 +249,19 @@
     <t>4135163187</t>
   </si>
   <si>
-    <t>13/03/2023</t>
-  </si>
-  <si>
     <t>4135163380</t>
   </si>
   <si>
-    <t>18628</t>
+    <t>4142401296</t>
   </si>
   <si>
     <t>Melhoria lançamento fiscal de consignados</t>
   </si>
   <si>
-    <t>14/03/2023</t>
-  </si>
-  <si>
-    <t>19234</t>
+    <t>20/03/2023</t>
+  </si>
+  <si>
+    <t>4157235654</t>
   </si>
   <si>
     <t>Alteração regra de preenchimento integração NF entrada para Benner</t>
@@ -255,19 +270,22 @@
     <t>16/03/2023</t>
   </si>
   <si>
+    <t>15/03/2023</t>
+  </si>
+  <si>
+    <t>4180144934</t>
+  </si>
+  <si>
     <t>Sistema para horas Parte 02</t>
   </si>
   <si>
-    <t>21/03/2023</t>
-  </si>
-  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-06</t>
+    <t>Jun/2021</t>
   </si>
   <si>
     <t>Base</t>
@@ -912,7 +930,7 @@
         <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -921,33 +939,33 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
@@ -959,7 +977,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -968,15 +986,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -988,10 +1006,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>32</v>
@@ -1003,7 +1021,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1015,15 +1033,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1035,10 +1053,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>32</v>
@@ -1050,7 +1068,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
@@ -1062,15 +1080,15 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1082,10 +1100,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>32</v>
@@ -1097,10 +1115,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1109,15 +1127,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1129,10 +1147,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>32</v>
@@ -1144,10 +1162,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1156,15 +1174,15 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1176,10 +1194,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>32</v>
@@ -1191,10 +1209,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1203,15 +1221,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1223,10 +1241,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>32</v>
@@ -1238,10 +1256,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1250,15 +1268,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1270,10 +1288,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>32</v>
@@ -1285,10 +1303,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1297,15 +1315,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1317,10 +1335,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>32</v>
@@ -1332,10 +1350,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1344,15 +1362,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1364,10 +1382,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
@@ -1379,7 +1397,7 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
@@ -1391,30 +1409,30 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -1426,10 +1444,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1438,15 +1456,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1458,10 +1476,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>32</v>
@@ -1473,10 +1491,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1485,33 +1503,33 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1520,10 +1538,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1532,33 +1550,33 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1567,10 +1585,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1579,15 +1597,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1599,10 +1617,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>32</v>
@@ -1614,10 +1632,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1626,15 +1644,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1646,10 +1664,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>32</v>
@@ -1661,10 +1679,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1676,12 +1694,12 @@
         <v>27</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1693,10 +1711,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>32</v>
@@ -1708,7 +1726,7 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>24</v>
@@ -1723,7 +1741,7 @@
         <v>27</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1739,23 +1757,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -1763,16 +1781,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1783,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>46.37</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -1791,7 +1809,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -1804,7 +1822,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1812,7 +1830,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1843,12 +1861,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B2">
         <v>19</v>
@@ -1862,7 +1880,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -1872,25 +1890,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1907,13 +1925,13 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1925,21 +1943,21 @@
         <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1951,16 +1969,16 @@
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -1977,27 +1995,27 @@
         <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2009,27 +2027,21 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2037,7 +2049,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2045,7 +2057,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2053,7 +2065,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2061,10 +2073,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2072,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2080,142 +2092,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="2">
+        <v>630</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2">
+        <v>629</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>628</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
